--- a/logs/all_features_head_number/2_head_model_systematic_experiments_good_angle/2_head_model_systematic_good_angle.xlsx
+++ b/logs/all_features_head_number/2_head_model_systematic_experiments_good_angle/2_head_model_systematic_good_angle.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/2_head_model_systematic_experiments_good_angle/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/all_features_head_number/2_head_model_systematic_experiments_good_angle/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="79" documentId="11_05E1B2ABD35053C9A4A91FD04B5ED87656CF0F5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CDC1652-35FB-46D0-8361-4906E17676FD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="11" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -690,7 +690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -700,7 +700,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6653,7 +6652,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A178BD3-3D75-4ACA-832E-2B46CB0D386F}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A178BD3-3D75-4ACA-832E-2B46CB0D386F}" name="TablaDinámica1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:N11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="78">
     <pivotField numFmtId="164" showAll="0"/>
@@ -6871,7 +6870,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{435B1712-0BA8-4A82-B815-4D11FED636C2}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{435B1712-0BA8-4A82-B815-4D11FED636C2}" name="TablaDinámica1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="78">
     <pivotField numFmtId="164" showAll="0"/>
@@ -7048,7 +7047,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24F1B064-73C0-4A58-B504-4B148F38E2C6}" name="TablaDinámica2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24F1B064-73C0-4A58-B504-4B148F38E2C6}" name="TablaDinámica2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A2:G6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="78">
     <pivotField numFmtId="164" showAll="0"/>
@@ -17533,11 +17532,11 @@
       <c r="BX42">
         <v>6.5556342856279759E-2</v>
       </c>
-      <c r="BY42" s="5" t="str">
+      <c r="BY42" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ42" s="5" t="str">
+      <c r="BZ42" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -17768,11 +17767,11 @@
       <c r="BX43">
         <v>-1.0103931106445361</v>
       </c>
-      <c r="BY43" s="5" t="str">
+      <c r="BY43" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ43" s="5" t="str">
+      <c r="BZ43" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -18003,11 +18002,11 @@
       <c r="BX44">
         <v>-8.7997990674270277E-2</v>
       </c>
-      <c r="BY44" s="5" t="str">
+      <c r="BY44" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ44" s="5" t="str">
+      <c r="BZ44" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -18238,11 +18237,11 @@
       <c r="BX45">
         <v>-5.213181686223356E-2</v>
       </c>
-      <c r="BY45" s="5" t="str">
+      <c r="BY45" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ45" s="5" t="str">
+      <c r="BZ45" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -18473,11 +18472,11 @@
       <c r="BX46">
         <v>-7.3668147400131501E-2</v>
       </c>
-      <c r="BY46" s="5" t="str">
+      <c r="BY46" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ46" s="5" t="str">
+      <c r="BZ46" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -18708,11 +18707,11 @@
       <c r="BX47">
         <v>-0.245195645446975</v>
       </c>
-      <c r="BY47" s="5" t="str">
+      <c r="BY47" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ47" s="5" t="str">
+      <c r="BZ47" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -18943,11 +18942,11 @@
       <c r="BX48">
         <v>-0.47096045888316079</v>
       </c>
-      <c r="BY48" s="5" t="str">
+      <c r="BY48" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ48" s="5" t="str">
+      <c r="BZ48" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -19178,11 +19177,11 @@
       <c r="BX49">
         <v>-0.50875949756077654</v>
       </c>
-      <c r="BY49" s="5" t="str">
+      <c r="BY49" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ49" s="5" t="str">
+      <c r="BZ49" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -19413,11 +19412,11 @@
       <c r="BX50">
         <v>-0.49752968384612761</v>
       </c>
-      <c r="BY50" s="5" t="str">
+      <c r="BY50" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ50" s="5" t="str">
+      <c r="BZ50" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -19648,11 +19647,11 @@
       <c r="BX51">
         <v>-0.59986510349829669</v>
       </c>
-      <c r="BY51" s="5" t="str">
+      <c r="BY51" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ51" s="5" t="str">
+      <c r="BZ51" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -19883,11 +19882,11 @@
       <c r="BX52">
         <v>-0.26434830983501539</v>
       </c>
-      <c r="BY52" s="5" t="str">
+      <c r="BY52" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ52" s="5" t="str">
+      <c r="BZ52" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -20118,11 +20117,11 @@
       <c r="BX53">
         <v>-0.17648318291548559</v>
       </c>
-      <c r="BY53" s="5" t="str">
+      <c r="BY53" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ53" s="5" t="str">
+      <c r="BZ53" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -20353,11 +20352,11 @@
       <c r="BX54">
         <v>-9.4126135118296483E-2</v>
       </c>
-      <c r="BY54" s="5" t="str">
+      <c r="BY54" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ54" s="5" t="str">
+      <c r="BZ54" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -20588,11 +20587,11 @@
       <c r="BX55">
         <v>0.1106198192762283</v>
       </c>
-      <c r="BY55" s="5" t="str">
+      <c r="BY55" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ55" s="5" t="str">
+      <c r="BZ55" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -20823,11 +20822,11 @@
       <c r="BX56">
         <v>-0.13535798157527551</v>
       </c>
-      <c r="BY56" s="5" t="str">
+      <c r="BY56" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ56" s="5" t="str">
+      <c r="BZ56" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -21058,11 +21057,11 @@
       <c r="BX57">
         <v>-0.29951618875795832</v>
       </c>
-      <c r="BY57" s="5" t="str">
+      <c r="BY57" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ57" s="5" t="str">
+      <c r="BZ57" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -21293,11 +21292,11 @@
       <c r="BX58">
         <v>5.8943994832009072E-2</v>
       </c>
-      <c r="BY58" s="5" t="str">
+      <c r="BY58" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ58" s="5" t="str">
+      <c r="BZ58" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -21528,11 +21527,11 @@
       <c r="BX59">
         <v>-0.26400695806137692</v>
       </c>
-      <c r="BY59" s="5" t="str">
+      <c r="BY59" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ59" s="5" t="str">
+      <c r="BZ59" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -21763,11 +21762,11 @@
       <c r="BX60">
         <v>-0.1430433276581555</v>
       </c>
-      <c r="BY60" s="5" t="str">
+      <c r="BY60" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ60" s="5" t="str">
+      <c r="BZ60" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -21998,11 +21997,11 @@
       <c r="BX61">
         <v>-0.47560617147592832</v>
       </c>
-      <c r="BY61" s="5" t="str">
+      <c r="BY61" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ61" s="5" t="str">
+      <c r="BZ61" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -22233,11 +22232,11 @@
       <c r="BX62">
         <v>-0.40165384019986239</v>
       </c>
-      <c r="BY62" s="5" t="str">
+      <c r="BY62" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ62" s="5" t="str">
+      <c r="BZ62" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -22468,11 +22467,11 @@
       <c r="BX63">
         <v>-0.26872357927497892</v>
       </c>
-      <c r="BY63" s="5" t="str">
+      <c r="BY63" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ63" s="5" t="str">
+      <c r="BZ63" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -22703,11 +22702,11 @@
       <c r="BX64">
         <v>-0.16288230077323559</v>
       </c>
-      <c r="BY64" s="5" t="str">
+      <c r="BY64" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ64" s="5" t="str">
+      <c r="BZ64" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -22938,11 +22937,11 @@
       <c r="BX65">
         <v>-4.1660157074527193E-2</v>
       </c>
-      <c r="BY65" s="5" t="str">
+      <c r="BY65" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ65" s="5" t="str">
+      <c r="BZ65" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -23173,11 +23172,11 @@
       <c r="BX66">
         <v>-0.1023395119888659</v>
       </c>
-      <c r="BY66" s="5" t="str">
+      <c r="BY66" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ66" s="5" t="str">
+      <c r="BZ66" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -23408,11 +23407,11 @@
       <c r="BX67">
         <v>-0.35385523733974572</v>
       </c>
-      <c r="BY67" s="5" t="str">
+      <c r="BY67" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ67" s="5" t="str">
+      <c r="BZ67" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -23643,11 +23642,11 @@
       <c r="BX68">
         <v>-0.88018371752660274</v>
       </c>
-      <c r="BY68" s="5" t="str">
+      <c r="BY68" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ68" s="5" t="str">
+      <c r="BZ68" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -23878,11 +23877,11 @@
       <c r="BX69">
         <v>-0.35692711261288901</v>
       </c>
-      <c r="BY69" s="5" t="str">
+      <c r="BY69" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>2, 3, 4</v>
       </c>
-      <c r="BZ69" s="5" t="str">
+      <c r="BZ69" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -24113,11 +24112,11 @@
       <c r="BX70">
         <v>-0.21217879371636481</v>
       </c>
-      <c r="BY70" s="5" t="str">
+      <c r="BY70" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ70" s="5" t="str">
+      <c r="BZ70" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>1, 4, 0</v>
       </c>
@@ -24348,11 +24347,11 @@
       <c r="BX71">
         <v>-0.46372710863255318</v>
       </c>
-      <c r="BY71" s="5" t="str">
+      <c r="BY71" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),300,300))," ",", ")</f>
         <v>3, 4, 2</v>
       </c>
-      <c r="BZ71" s="5" t="str">
+      <c r="BZ71" t="str">
         <f>SUBSTITUTE(TRIM(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Tabla1[[#This Row],[map]],"[",""),"]",""),",",REPT(" ",100)),901,300))," ",", ")</f>
         <v>0, 1, 4</v>
       </c>
@@ -24434,43 +24433,43 @@
       <c r="A4" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.7015284380626895</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>-0.47277609519724423</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>0.67521021028600736</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>-0.40334331822090858</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>0.54834297053149206</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4">
         <v>0.74921214267333314</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>0.72662824128597869</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.67665748665322556</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>-0.32322065015985235</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>0.11153430756312314</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>-1.0824397659136618</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4">
         <v>-0.31924716437324346</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4">
         <v>10</v>
       </c>
     </row>
@@ -24478,43 +24477,43 @@
       <c r="A5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>0.67872765761868203</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>-8.0650245790221994E-2</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>0.65778328172909029</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>1.2059263724309509E-2</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>0.52235163574375287</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>0.7504777876076526</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>0.79371240569866452</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.5645912978662917</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>-0.16751543149037357</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>0.26239543194621556</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>0.1846322785520505</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5">
         <v>-0.2312752241106531</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5">
         <v>10</v>
       </c>
     </row>
@@ -24522,43 +24521,43 @@
       <c r="A6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>0.67407491365092598</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>-0.11559068628256428</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>0.63908617441779259</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>-6.0069740151355841E-2</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>0.57928978164931011</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6">
         <v>0.75869931623206954</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>0.64427013286803381</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.5740854669217571</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>-7.8270268361069761E-2</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>0.11478341455432703</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>0.11808625513944933</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6">
         <v>-0.39487836193813008</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6">
         <v>10</v>
       </c>
     </row>
@@ -24566,43 +24565,43 @@
       <c r="A7" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>0.67087548513638051</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>-0.36900076952004895</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>0.62386146285028554</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>-0.30718261798589025</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>0.42478159640080432</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7">
         <v>0.67022903578207271</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>0.7172452153630311</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>0.68319000385523543</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>2.3711414011802011E-2</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>-0.20712675104989917</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>-0.79866364573867676</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>-0.24665148916678881</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7">
         <v>10</v>
       </c>
     </row>
@@ -24610,43 +24609,43 @@
       <c r="A8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>0.62638086040636953</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>-8.1158847672368431E-2</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>0.5884475977025625</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>-4.7731618767752559E-2</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>0.39770235797012932</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8">
         <v>0.62705966135911673</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>0.7934057697433976</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>0.53562260173760723</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>-0.28728551372144562</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8">
         <v>0.22350027730463062</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>0.1645818527316453</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>-0.2917230913858409</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8">
         <v>10</v>
       </c>
     </row>
@@ -24654,43 +24653,43 @@
       <c r="A9" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>0.65086997636830335</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>-9.3007430840882921E-5</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>0.5831840612149688</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>-1.73185596649429E-2</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>0.44847120155061349</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9">
         <v>0.67239169886118511</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>0.66569549749719104</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>0.54617784695088578</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>5.4000679352258628E-2</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9">
         <v>-8.8610858827261572E-3</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9">
         <v>0.16048760556957214</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9">
         <v>-0.27490143769887854</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9">
         <v>10</v>
       </c>
     </row>
@@ -24698,43 +24697,43 @@
       <c r="A10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>0.60746206263392355</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>-5.7914672058916983E-2</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>0.55314170359473636</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>1.7383656688629647E-2</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>0.36029909404099325</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10">
         <v>0.63920812676846861</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <v>0.64956995017863073</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10">
         <v>0.56348964339085295</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>-0.20629809249006908</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10">
         <v>0.42180256629672092</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10">
         <v>0.18608753287178917</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10">
         <v>-0.33205737992392442</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10">
         <v>10</v>
       </c>
     </row>
@@ -24742,43 +24741,43 @@
       <c r="A11" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>0.65855991341103914</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>-0.16816918913602941</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>0.61724492739934889</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>-0.11517184776827298</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>0.46874837684101361</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11">
         <v>0.69532539561198581</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <v>0.71293245894784663</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11">
         <v>0.59197347819655077</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>-0.14069683755124995</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11">
         <v>0.13114688010462741</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11">
         <v>-0.15246112668397599</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11">
         <v>-0.29867630694249436</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11">
         <v>70</v>
       </c>
     </row>
@@ -24828,22 +24827,22 @@
       <c r="A2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>0.54999479597485179</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2">
         <v>0.75279641550435195</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>-0.18966878333709858</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>0.16290438468788854</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2">
         <v>0.65735988881096341</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2">
         <v>-0.15045126488265165</v>
       </c>
     </row>
@@ -24851,22 +24850,22 @@
       <c r="A3" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>0.37900072600556123</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>0.6331338940637925</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>-0.24679180310575735</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>0.32265142180067574</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3">
         <v>0.57079465064864954</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3">
         <v>-1.5173981039561451E-2</v>
       </c>
     </row>
@@ -24874,22 +24873,22 @@
       <c r="A4" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.43662639897570898</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>0.67131036732162908</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>3.885604668203034E-2</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>-0.10799391846631268</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>0.60352276203262711</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4">
         <v>-0.1622505888254166</v>
       </c>
     </row>
@@ -24897,22 +24896,22 @@
       <c r="A5" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>0.4687483768410135</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>0.6953253956119857</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>-0.14069683755124998</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>0.13114688010462744</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>0.61724492739934889</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>-0.11517184776827301</v>
       </c>
     </row>
@@ -24961,22 +24960,22 @@
       <c r="A3" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>0.65317852684795197</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>0.5612509857544985</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>0.15488713119360356</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>-0.33394572652031101</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3">
         <v>0.59180397974249921</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3">
         <v>-2.0001547709223026E-2</v>
       </c>
     </row>
@@ -24984,22 +24983,22 @@
       <c r="A4" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.79355908772103123</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>0.5501069498019493</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>0.17460706564184791</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>-0.261499157748247</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>0.62311543971582617</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4">
         <v>-1.7836177521721525E-2</v>
       </c>
     </row>
@@ -25007,22 +25006,22 @@
       <c r="A5" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>0.72193672832450473</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>0.6799237452542306</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>-0.94055170582616898</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>-0.28294932677001616</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>0.64953583656814629</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>-0.35526296810339941</v>
       </c>
     </row>
@@ -25030,22 +25029,22 @@
       <c r="A6" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>0.71293245894784663</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>0.59197347819655088</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>-0.15246112668397596</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>-0.29867630694249431</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>0.617244927399349</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6">
         <v>-0.11517184776827301</v>
       </c>
     </row>
